--- a/data/reports/PHASE_6_PATTERN_ENGINE.xlsx
+++ b/data/reports/PHASE_6_PATTERN_ENGINE.xlsx
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
@@ -477,17 +477,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OEE</t>
+          <t>EEO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EEO</t>
+          <t>OEE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="3">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -851,17 +851,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LHH</t>
+          <t>HHH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HHH</t>
+          <t>LHH</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -871,17 +871,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LHL</t>
+          <t>LLH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLH</t>
+          <t>LHL</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1755"/>
+  <dimension ref="A1:F1757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57108,6 +57108,70 @@
         </is>
       </c>
     </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>Midday</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>EEO</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>LLH</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>EOE</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>LHL</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
